--- a/ToxCast_model/experiments/training/DART_MTL/results/training_results_template.xlsx
+++ b/ToxCast_model/experiments/training/DART_MTL/results/training_results_template.xlsx
@@ -84,7 +84,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -459,7 +459,7 @@
     <col min="17" max="17" style="3" width="13.005" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
